--- a/models/templates/performance-ratios-template.xlsx
+++ b/models/templates/performance-ratios-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MBA\BUS-629 Managerial Finance\Corporate-Finance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\shidler\docs\templates\spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2C0A1E4-6DD1-4821-B32D-AF579751EE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_C2087B7F3B7CCEACD4328DE2D1E5418A185D2F1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -1373,7 +1373,7 @@
     <xf numFmtId="49" fontId="18" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1381,7 +1381,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1682,26 +1682,6 @@
 </a:theme>
 </file>
 
-<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
-<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="525" row="1">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </wetp:taskpane>
-</wetp:taskpanes>
-</file>
-
-<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{A5397D9D-3B81-47F8-B52C-3326AE325E70}">
-  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
-  <we:alternateReferences>
-    <we:reference id="wa200009404" version="1.0.0.8" store="wa200009404" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties/>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</we:webextension>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:C41"/>
@@ -1718,7 +1698,7 @@
       <c r="C2" s="1"/>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="51" t="s">
         <v>157</v>
       </c>
       <c r="C4" s="46"/>
@@ -2750,7 +2730,7 @@
       </c>
     </row>
     <row r="14" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B14" s="51" t="s">
+      <c r="B14" s="45" t="s">
         <v>22</v>
       </c>
       <c r="C14" s="46"/>
@@ -2762,7 +2742,7 @@
         <v>23</v>
       </c>
       <c r="C15" s="36">
-        <f ca="1">avg_equity</f>
+        <f>BAL_equity_shareholders_prior</f>
         <v>0</v>
       </c>
       <c r="D15" s="30" t="s">
@@ -2833,7 +2813,7 @@
       </c>
     </row>
     <row r="21" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="51" t="s">
+      <c r="B21" s="45" t="s">
         <v>38</v>
       </c>
       <c r="C21" s="46"/>
@@ -3021,7 +3001,7 @@
       </c>
     </row>
     <row r="35" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B35" s="51" t="s">
+      <c r="B35" s="45" t="s">
         <v>75</v>
       </c>
       <c r="C35" s="46"/>
@@ -3033,7 +3013,7 @@
         <v>76</v>
       </c>
       <c r="C36" s="37">
-        <f ca="1">AVERAGE(startYear_equity,currentYear_equity)</f>
+        <f>AVERAGE(startYear_equity,currentYear_equity)</f>
         <v>0</v>
       </c>
       <c r="D36" s="30" t="s">
